--- a/Results/Alpha_Beta Ratio/Ratio_AO_Analysis.xlsx
+++ b/Results/Alpha_Beta Ratio/Ratio_AO_Analysis.xlsx
@@ -1403,13 +1403,13 @@
         <v>47</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1448</v>
+        <v>0.0303</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0512</v>
+        <v>0.0097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.263</v>
+        <v>0.0676</v>
       </c>
     </row>
     <row r="5">
@@ -1417,13 +1417,13 @@
         <v>48</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1839</v>
+        <v>0.0272</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0676</v>
+        <v>0.0083</v>
       </c>
       <c r="D5" t="n">
-        <v>0.329</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="6">
@@ -1431,13 +1431,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1259</v>
+        <v>0.0202</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0397</v>
+        <v>0.006</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2335</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="7">
@@ -1470,19 +1470,19 @@
         <v>55</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0369</v>
+        <v>0.003</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1074</v>
+        <v>-0.0131</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0168</v>
+        <v>0.0213</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1008</v>
+        <v>0.6628</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8992</v>
+        <v>0.3372</v>
       </c>
     </row>
     <row r="10">
@@ -1490,19 +1490,19 @@
         <v>56</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0176</v>
+        <v>0.0092</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0346</v>
+        <v>-0.004</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0719</v>
+        <v>0.0309</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7842</v>
+        <v>0.939</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2158</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="11">
@@ -1510,19 +1510,19 @@
         <v>57</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0553</v>
+        <v>0.0064</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0056</v>
+        <v>-0.0067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.119</v>
+        <v>0.0234</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9878</v>
+        <v>0.8965</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0122</v>
+        <v>0.1035</v>
       </c>
     </row>
   </sheetData>
@@ -1565,13 +1565,13 @@
         <v>60</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1773</v>
+        <v>0.0306</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0441</v>
+        <v>0.0073</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3631</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="5">
@@ -1579,13 +1579,13 @@
         <v>61</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1138</v>
+        <v>0.0189</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0167</v>
+        <v>0.0035</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2618</v>
+        <v>0.0498</v>
       </c>
     </row>
     <row r="6">
@@ -1618,19 +1618,19 @@
         <v>63</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0611</v>
+        <v>0.0111</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1659</v>
+        <v>-0.0332</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2753</v>
+        <v>0.0628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7278</v>
+        <v>0.7452</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2722</v>
+        <v>0.2547</v>
       </c>
     </row>
   </sheetData>
@@ -1679,13 +1679,13 @@
         <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>0.194</v>
+        <v>0.0418</v>
       </c>
       <c r="D4" t="n">
-        <v>0.044</v>
+        <v>0.0094</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3943</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="5">
@@ -1696,13 +1696,13 @@
         <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0817</v>
+        <v>0.0159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0078</v>
+        <v>0.0026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2078</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="6">
@@ -1713,13 +1713,13 @@
         <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2013</v>
+        <v>0.0287</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0508</v>
+        <v>0.0058</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4113</v>
+        <v>0.0766</v>
       </c>
     </row>
     <row r="7">
@@ -1730,13 +1730,13 @@
         <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1517</v>
+        <v>0.0226</v>
       </c>
       <c r="D7" t="n">
-        <v>0.024</v>
+        <v>0.0038</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3347</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="8">
@@ -1747,13 +1747,13 @@
         <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1325</v>
+        <v>0.0206</v>
       </c>
       <c r="D8" t="n">
-        <v>0.028</v>
+        <v>0.0043</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2981</v>
+        <v>0.0544</v>
       </c>
     </row>
     <row r="9">
@@ -1764,13 +1764,13 @@
         <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1058</v>
+        <v>0.0176</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0137</v>
+        <v>0.003</v>
       </c>
       <c r="E9" t="n">
-        <v>0.256</v>
+        <v>0.0496</v>
       </c>
     </row>
     <row r="10">
@@ -1809,19 +1809,19 @@
         <v>47</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1054</v>
+        <v>0.0245</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0996</v>
+        <v>-0.0201</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3401</v>
+        <v>0.0953</v>
       </c>
       <c r="F12" t="n">
-        <v>0.869</v>
+        <v>0.895</v>
       </c>
       <c r="G12" t="n">
-        <v>0.131</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="13">
@@ -1832,19 +1832,19 @@
         <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0489</v>
+        <v>0.0058</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2195</v>
+        <v>-0.0423</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2985</v>
+        <v>0.0647</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6595</v>
+        <v>0.629</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3405</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="14">
@@ -1855,19 +1855,19 @@
         <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0246</v>
+        <v>0.0025</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1585</v>
+        <v>-0.0406</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2517</v>
+        <v>0.0414</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6115</v>
+        <v>0.5755</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3885</v>
+        <v>0.4245</v>
       </c>
     </row>
     <row r="15">
@@ -1906,19 +1906,19 @@
         <v>60</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0045</v>
+        <v>0.012</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1014</v>
+        <v>-0.0107</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0731</v>
+        <v>0.0463</v>
       </c>
       <c r="F17" t="n">
-        <v>0.454</v>
+        <v>0.8895</v>
       </c>
       <c r="G17" t="n">
-        <v>0.546</v>
+        <v>0.1105</v>
       </c>
     </row>
     <row r="18">
@@ -1929,19 +1929,19 @@
         <v>60</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0574</v>
+        <v>0.0202</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0112</v>
+        <v>0.0006</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1446</v>
+        <v>0.0579</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9612</v>
+        <v>0.9935</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0388</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="19">
@@ -1952,19 +1952,19 @@
         <v>60</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0639</v>
+        <v>0.0074</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0079</v>
+        <v>-0.0093</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1554</v>
+        <v>0.0349</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9692</v>
+        <v>0.872</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0307</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="20">
@@ -1975,19 +1975,19 @@
         <v>61</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0639</v>
+        <v>-0.0057</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1611</v>
+        <v>-0.0261</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0047</v>
+        <v>0.005</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005</v>
+        <v>0.1143</v>
       </c>
       <c r="G20" t="n">
-        <v>0.995</v>
+        <v>0.8858</v>
       </c>
     </row>
     <row r="21">
@@ -1998,19 +1998,19 @@
         <v>61</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0204</v>
+        <v>-0.0016</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0856</v>
+        <v>-0.0145</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0226</v>
+        <v>0.0124</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1185</v>
+        <v>0.3238</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8815</v>
+        <v>0.6762</v>
       </c>
     </row>
     <row r="22">
@@ -2021,19 +2021,19 @@
         <v>61</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0416</v>
+        <v>0.0041</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0105</v>
+        <v>-0.0088</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1251</v>
+        <v>0.0239</v>
       </c>
       <c r="F22" t="n">
-        <v>0.947</v>
+        <v>0.809</v>
       </c>
       <c r="G22" t="n">
-        <v>0.053</v>
+        <v>0.191</v>
       </c>
     </row>
   </sheetData>
@@ -2087,13 +2087,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0619</v>
+        <v>-0.0133</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1072</v>
+        <v>-0.026</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0041</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2132,19 +2132,19 @@
         <v>47</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0525</v>
+        <v>-0.0139</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.095</v>
+        <v>-0.0279</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0172</v>
+        <v>-0.0045</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2152,13 +2152,13 @@
         <v>48</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.075</v>
+        <v>-0.0136</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1238</v>
+        <v>-0.0283</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0283</v>
+        <v>-0.0041</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0578</v>
+        <v>-0.0121</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1061</v>
+        <v>-0.0254</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0224</v>
+        <v>-0.0037</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2217,19 +2217,19 @@
         <v>55</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0209</v>
+        <v>-0.0003</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0451</v>
+        <v>0.007</v>
       </c>
       <c r="E14" t="n">
-        <v>0.979</v>
+        <v>0.4658</v>
       </c>
       <c r="F14" t="n">
-        <v>0.021</v>
+        <v>0.5342</v>
       </c>
     </row>
     <row r="15">
@@ -2237,19 +2237,19 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0048</v>
+        <v>-0.0016</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0122</v>
+        <v>-0.0093</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0253</v>
+        <v>0.0051</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7153</v>
+        <v>0.276</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2848</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="16">
@@ -2257,19 +2257,19 @@
         <v>57</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0158</v>
+        <v>-0.0014</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0381</v>
+        <v>-0.0078</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0039</v>
+        <v>0.0047</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06</v>
+        <v>0.3015</v>
       </c>
       <c r="F16" t="n">
-        <v>0.94</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="17">
@@ -2302,19 +2302,19 @@
         <v>60</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.0546</v>
+        <v>-0.0118</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.107</v>
+        <v>-0.0276</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0138</v>
+        <v>-0.0024</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0013</v>
+        <v>0.0015</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9988</v>
+        <v>0.9985</v>
       </c>
     </row>
     <row r="20">
@@ -2322,13 +2322,13 @@
         <v>61</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.0658</v>
+        <v>-0.0135</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1371</v>
+        <v>-0.0347</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0088</v>
+        <v>-0.0012</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2367,19 +2367,19 @@
         <v>63</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0106</v>
+        <v>0.0013</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.068</v>
+        <v>-0.0214</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0946</v>
+        <v>0.0277</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61</v>
+        <v>0.5582</v>
       </c>
       <c r="F23" t="n">
-        <v>0.39</v>
+        <v>0.4417</v>
       </c>
     </row>
   </sheetData>
@@ -2433,19 +2433,19 @@
         <v>22</v>
       </c>
       <c r="B5" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.0064</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.0116</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0257</v>
-      </c>
       <c r="E5" t="n">
-        <v>0.784</v>
+        <v>0.668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.216</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="7">
@@ -2478,19 +2478,19 @@
         <v>47</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0037</v>
+        <v>0.0009</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0155</v>
+        <v>-0.0044</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0202</v>
+        <v>0.0076</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6898</v>
+        <v>0.6632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3103</v>
+        <v>0.3368</v>
       </c>
     </row>
     <row r="10">
@@ -2498,19 +2498,19 @@
         <v>48</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0106</v>
+        <v>0.0015</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0113</v>
+        <v>-0.0044</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0301</v>
+        <v>0.0083</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8555</v>
+        <v>0.7505</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1445</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="11">
@@ -2518,19 +2518,19 @@
         <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0051</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0134</v>
+        <v>-0.0048</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0234</v>
+        <v>0.0048</v>
       </c>
       <c r="E11" t="n">
-        <v>0.743</v>
+        <v>0.5085</v>
       </c>
       <c r="F11" t="n">
-        <v>0.257</v>
+        <v>0.4915</v>
       </c>
     </row>
     <row r="12">
@@ -2563,19 +2563,19 @@
         <v>55</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.007</v>
+        <v>-0.0005</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0151</v>
+        <v>-0.004</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006</v>
+        <v>0.0023</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0405</v>
+        <v>0.322</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9595</v>
+        <v>0.678</v>
       </c>
     </row>
     <row r="15">
@@ -2583,19 +2583,19 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0013</v>
+        <v>0.0009</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0077</v>
+        <v>-0.0012</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0051</v>
+        <v>0.0043</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3285</v>
+        <v>0.8205</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6715</v>
+        <v>0.1795</v>
       </c>
     </row>
     <row r="16">
@@ -2603,19 +2603,19 @@
         <v>57</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0056</v>
+        <v>0.0014</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0007</v>
+        <v>-0.0006</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0127</v>
+        <v>0.0055</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9515</v>
+        <v>0.9355</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0485</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="17">
@@ -2648,19 +2648,19 @@
         <v>60</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02</v>
+        <v>0.0037</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0024</v>
+        <v>-0.0007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0441</v>
+        <v>0.0127</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9965</v>
+        <v>0.982</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0035</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="20">
@@ -2668,19 +2668,19 @@
         <v>61</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.0063</v>
+        <v>-0.002</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0375</v>
+        <v>-0.0102</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0127</v>
+        <v>0.0027</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2542</v>
+        <v>0.1457</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7458</v>
+        <v>0.8542</v>
       </c>
     </row>
     <row r="21">
@@ -2713,19 +2713,19 @@
         <v>63</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0281</v>
+        <v>0.0064</v>
       </c>
       <c r="C23" t="n">
         <v>-0.0002</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0625</v>
+        <v>0.0198</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9902</v>
+        <v>0.9858</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0098</v>
+        <v>0.0142</v>
       </c>
     </row>
   </sheetData>
@@ -2779,19 +2779,19 @@
         <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0078</v>
+        <v>0.0031</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0019</v>
+        <v>0.0004</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0195</v>
+        <v>0.0083</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9368</v>
+        <v>0.996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0632</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         <v>47</v>
       </c>
       <c r="B9" t="n">
-        <v>0.009</v>
+        <v>0.0024</v>
       </c>
       <c r="C9" t="n">
         <v>-0.0007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0225</v>
+        <v>0.0072</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9705</v>
+        <v>0.969</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0295</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="10">
@@ -2844,19 +2844,19 @@
         <v>48</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0044</v>
+        <v>0.0032</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0146</v>
+        <v>-0.0001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0063</v>
+        <v>0.0092</v>
       </c>
       <c r="E10" t="n">
-        <v>0.222</v>
+        <v>0.9802</v>
       </c>
       <c r="F10" t="n">
-        <v>0.778</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="11">
@@ -2864,13 +2864,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0183</v>
+        <v>0.0036</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0058</v>
+        <v>0.0007</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0334</v>
+        <v>0.0094</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2909,19 +2909,19 @@
         <v>55</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0137</v>
+        <v>-0.0007</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0037</v>
+        <v>-0.0042</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0238</v>
+        <v>0.002</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.278</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="15">
@@ -2929,19 +2929,19 @@
         <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0089</v>
+        <v>-0.0011</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0163</v>
+        <v>-0.0043</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0022</v>
+        <v>0.0012</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0005</v>
+        <v>0.1383</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9995</v>
+        <v>0.8618</v>
       </c>
     </row>
     <row r="16">
@@ -2949,19 +2949,19 @@
         <v>57</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0229</v>
+        <v>-0.0004</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0365</v>
+        <v>-0.0037</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0108</v>
+        <v>0.0028</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.615</v>
       </c>
     </row>
     <row r="17">
@@ -2994,19 +2994,19 @@
         <v>60</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.0104</v>
+        <v>-0.0006</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0167</v>
+        <v>-0.0023</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0037</v>
+        <v>0.0005</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.1098</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.8902</v>
       </c>
     </row>
     <row r="20">
@@ -3014,13 +3014,13 @@
         <v>61</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0261</v>
+        <v>0.0069</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0077</v>
+        <v>0.0011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0479</v>
+        <v>0.0166</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -3059,13 +3059,13 @@
         <v>63</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.0364</v>
+        <v>-0.0076</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0587</v>
+        <v>-0.0177</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0157</v>
+        <v>-0.0015</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -3136,13 +3136,13 @@
         <v>88</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0527</v>
+        <v>-0.014</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0996</v>
+        <v>-0.0292</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0195</v>
+        <v>-0.0042</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3159,13 +3159,13 @@
         <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0723</v>
+        <v>-0.0132</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1212</v>
+        <v>-0.0291</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0261</v>
+        <v>-0.0033</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3182,13 +3182,13 @@
         <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0564</v>
+        <v>-0.0123</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1038</v>
+        <v>-0.0274</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0199</v>
+        <v>-0.0033</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3205,19 +3205,19 @@
         <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0521</v>
+        <v>-0.0139</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0949</v>
+        <v>-0.0274</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0183</v>
+        <v>-0.0046</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3228,13 +3228,13 @@
         <v>89</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0773</v>
+        <v>-0.0141</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1272</v>
+        <v>-0.0284</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0308</v>
+        <v>-0.0041</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3251,13 +3251,13 @@
         <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0596</v>
+        <v>-0.0121</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1048</v>
+        <v>-0.0242</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0207</v>
+        <v>-0.0038</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3302,19 +3302,19 @@
         <v>91</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0089</v>
+        <v>-0.0049</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0137</v>
+        <v>0.0062</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5532</v>
+        <v>0.5002</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4468</v>
+        <v>0.4998</v>
       </c>
     </row>
     <row r="15">
@@ -3325,19 +3325,19 @@
         <v>91</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0047</v>
+        <v>-0.0009</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0161</v>
+        <v>-0.0058</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0078</v>
+        <v>0.0054</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2345</v>
+        <v>0.3465</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7655</v>
+        <v>0.6535</v>
       </c>
     </row>
     <row r="16">
@@ -3348,19 +3348,19 @@
         <v>91</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0036</v>
+        <v>0.0001</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0148</v>
+        <v>-0.0049</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0096</v>
+        <v>0.0063</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2708</v>
+        <v>0.5205</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7292</v>
+        <v>0.4795</v>
       </c>
     </row>
   </sheetData>
@@ -3425,19 +3425,19 @@
         <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0482</v>
+        <v>-0.0124</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0893</v>
+        <v>-0.0251</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.016</v>
+        <v>-0.0039</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3448,13 +3448,13 @@
         <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.079</v>
+        <v>-0.0128</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1303</v>
+        <v>-0.0266</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0323</v>
+        <v>-0.004</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3471,13 +3471,13 @@
         <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.05</v>
+        <v>-0.0098</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0944</v>
+        <v>-0.0206</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0164</v>
+        <v>-0.0029</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3494,13 +3494,13 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0573</v>
+        <v>-0.0159</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1028</v>
+        <v>-0.0314</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0215</v>
+        <v>-0.0048</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3517,13 +3517,13 @@
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0708</v>
+        <v>-0.0146</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1167</v>
+        <v>-0.0307</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0249</v>
+        <v>-0.0043</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>96</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0664</v>
+        <v>-0.0153</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.112</v>
+        <v>-0.0317</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0241</v>
+        <v>-0.0046</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -3591,19 +3591,19 @@
         <v>97</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.009</v>
+        <v>-0.0032</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0156</v>
+        <v>-0.0084</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0014</v>
+        <v>0.0003</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0107</v>
+        <v>0.0132</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9892</v>
+        <v>0.9868</v>
       </c>
     </row>
     <row r="15">
@@ -3614,19 +3614,19 @@
         <v>97</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0086</v>
+        <v>-0.0019</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0021</v>
+        <v>-0.0073</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0148</v>
+        <v>0.0018</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9962</v>
+        <v>0.1568</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0037</v>
+        <v>0.8433</v>
       </c>
     </row>
     <row r="16">
@@ -3637,19 +3637,19 @@
         <v>97</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0158</v>
+        <v>-0.0053</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0232</v>
+        <v>-0.012</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0067</v>
+        <v>-0.001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
